--- a/results/q4_output/情景对比汇总.xlsx
+++ b/results/q4_output/情景对比汇总.xlsx
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>164.5</v>
+        <v>31.6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8898</v>
+        <v>0.843</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>179.8</v>
+        <v>34.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9102</v>
+        <v>0.8429</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>195.8</v>
+        <v>37.6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9286</v>
+        <v>0.8429</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/q4_output/情景对比汇总.xlsx
+++ b/results/q4_output/情景对比汇总.xlsx
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31.6</v>
+        <v>161.8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.843</v>
+        <v>0.8218</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34.5</v>
+        <v>176.8</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8429</v>
+        <v>0.8969</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37.6</v>
+        <v>192.5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8429</v>
+        <v>0.9039</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/results/q4_output/情景对比汇总.xlsx
+++ b/results/q4_output/情景对比汇总.xlsx
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>161.8</v>
+        <v>164.9</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8218</v>
+        <v>0.8855</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -504,16 +504,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>176.8</v>
+        <v>180.2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8969</v>
+        <v>0.8778</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>192.5</v>
+        <v>196.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9039</v>
+        <v>0.8558</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
         <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
